--- a/data/trans_camb/P1804_2016_2023-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1804_2016_2023-Edad-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-5,7</t>
+          <t>-5,57</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,41</t>
+          <t>-2,96</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,59; -2,37</t>
+          <t>-8,28; -1,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 5,51</t>
+          <t>-4,24; 5,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,2; -0,22</t>
+          <t>-5,55; 0,29</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-86,37%</t>
+          <t>-84,3%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-3,15%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-45,58%</t>
+          <t>-39,54%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -22,33</t>
+          <t>-100,0; 18,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,69; 79,98</t>
+          <t>-45,84; 85,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-72,11; -2,91</t>
+          <t>-65,64; 6,27</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>2,95</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-1,19</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>1,9</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 7,02</t>
+          <t>-0,71; 7,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 2,88</t>
+          <t>-3,43; 4,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 4,01</t>
+          <t>-1,2; 4,76</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-11,42%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 189,89</t>
+          <t>-14,99; 202,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-49,24; 29,83</t>
+          <t>-26,51; 58,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 59,35</t>
+          <t>-14,66; 72,41</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-0,07</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,78</t>
+          <t>-1,6; 3,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,75</t>
+          <t>-4,17; 1,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,92</t>
+          <t>-2,04; 1,97</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-13,1%</t>
+          <t>-11,33%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-2,14%</t>
+          <t>-1,04%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 131,71</t>
+          <t>-33,1; 117,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,8; 23,48</t>
+          <t>-38,17; 21,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 35,86</t>
+          <t>-27,62; 36,84</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>1,51</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 2,94</t>
+          <t>-1,03; 5,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,98</t>
+          <t>-1,26; 3,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,05</t>
+          <t>-0,22; 3,39</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-8,85%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-1,64%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-61,45; 65,19</t>
+          <t>-17,63; 131,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 60,65</t>
+          <t>-16,06; 73,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,6; 40,01</t>
+          <t>-4,32; 71,23</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-2,34</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-1,58</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 2,4</t>
+          <t>-4,08; 2,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 0,49</t>
+          <t>-6,17; 0,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,54</t>
+          <t>-4,04; 0,62</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-12,73%</t>
+          <t>-9,53%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-25,17%</t>
+          <t>-21,69%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-20,2%</t>
+          <t>-16,78%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 42,04</t>
+          <t>-40,91; 38,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,64; 6,07</t>
+          <t>-44,91; 12,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-38,53; 7,39</t>
+          <t>-35,66; 9,08</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-2,79</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-6,12</t>
+          <t>-3,34</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-4,83</t>
+          <t>-3,15</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 0,98</t>
+          <t>-6,76; 1,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,22; -2,04</t>
+          <t>-7,47; 0,26</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -1,78</t>
+          <t>-5,94; -0,28</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-25,01%</t>
+          <t>-26,26%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-53,14%</t>
+          <t>-28,98%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-42,57%</t>
+          <t>-27,72%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 14,35</t>
+          <t>-48,89; 12,34</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-85,14; -19,82</t>
+          <t>-51,93; 2,57</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-70,3; -17,71</t>
+          <t>-44,53; -1,98</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-2,05</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-7,01</t>
+          <t>-6,91</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-5,02</t>
+          <t>-5,03</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 1,74</t>
+          <t>-6,19; 1,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,95; -2,21</t>
+          <t>-12,01; -2,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,59; -1,84</t>
+          <t>-8,41; -2,14</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-21,04%</t>
+          <t>-22,78%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-44,83%</t>
+          <t>-44,23%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-38,49%</t>
+          <t>-38,56%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-52,21; 29,45</t>
+          <t>-52,71; 29,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-59,97; -17,84</t>
+          <t>-60,53; -20,03</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-54,63; -16,42</t>
+          <t>-54,04; -18,8</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-2,36</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>-0,76</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,59</t>
+          <t>-1,3; 1,28</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,95</t>
+          <t>-2,86; -0,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,7; -0,59</t>
+          <t>-1,77; 0,13</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-12,39%</t>
+          <t>-1,72%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-23,8%</t>
+          <t>-14,13%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-19,41%</t>
+          <t>-9,37%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 10,24</t>
+          <t>-18,84; 21,92</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-38,52; -10,13</t>
+          <t>-26,97; -1,46</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-31,65; -7,88</t>
+          <t>-19,86; 1,92</t>
         </is>
       </c>
     </row>
